--- a/Tech_Products_Sales_Data.xlsx
+++ b/Tech_Products_Sales_Data.xlsx
@@ -2,25 +2,89 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Krishna_Anuj_DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB971D6-5EDB-43D8-B2FC-DAD6E07C58AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB72C9C-7384-4FD1-BF0D-6F959D56DB6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="hidden" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{FD8E434A-CA42-4556-B8E0-0EF636BCDB99}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{D45996A5-4960-4DD4-9A4C-68BBCD2937B6}"/>
   </bookViews>
   <sheets>
     <sheet name="TechyStore Sales_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$K$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">Sheet1!$1:$1</definedName>
+    <definedName name="Z_348453C5_8389_40E9_BA80_3FA4E537F326_.wvu.FilterData" localSheetId="1" hidden="1">Sheet2!$A$1:$K$35</definedName>
+    <definedName name="Z_54F2BD4B_57B8_4870_9A16_CEBD580B8381_.wvu.FilterData" localSheetId="1" hidden="1">Sheet2!$A$1:$K$35</definedName>
+    <definedName name="Z_554D4A35_920F_4EF4_A143_68894776BCD6_.wvu.FilterData" localSheetId="1" hidden="1">Sheet2!$A$1:$K$35</definedName>
+    <definedName name="Z_554D4A35_920F_4EF4_A143_68894776BCD6_.wvu.PrintTitles" localSheetId="2" hidden="1">Sheet1!$1:$1</definedName>
+    <definedName name="Z_554D4A35_920F_4EF4_A143_68894776BCD6_.wvu.Rows" localSheetId="1" hidden="1">Sheet2!$26:$35</definedName>
+    <definedName name="Z_FC9649D9_9489_4BAB_903C_EF400B6D7A4B_.wvu.FilterData" localSheetId="1" hidden="1">Sheet2!$A$1:$K$35</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <customWorkbookViews>
+    <customWorkbookView name="pc - Personal View" guid="{554D4A35-920F-4EF4-A143-68894776BCD6}" mergeInterval="0" personalView="1" maximized="1" xWindow="-9" yWindow="-9" windowWidth="1938" windowHeight="1048" activeSheetId="2"/>
+  </customWorkbookViews>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>pc</author>
+  </authors>
+  <commentList>
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{29AE6876-F23F-4F55-8BC9-C0A81B3F9A9F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Online shop</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{69A9C974-EAE3-4E01-BA15-634BFECBA85F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>pc:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+New Compute this state in india</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9012" uniqueCount="2690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10474" uniqueCount="2695">
   <si>
     <t>Transaction ID</t>
   </si>
@@ -8090,17 +8154,32 @@
   </si>
   <si>
     <t>Cash</t>
+  </si>
+  <si>
+    <t>Total sale</t>
+  </si>
+  <si>
+    <t>dsg</t>
+  </si>
+  <si>
+    <t>vfd</t>
+  </si>
+  <si>
+    <t>Shivani</t>
+  </si>
+  <si>
+    <t>dgf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Corbel"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -8108,9 +8187,22 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Corbel"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -8133,7 +8225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -8142,6 +8234,15 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8160,9 +8261,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Wisp">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Yellow">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8170,100 +8271,48 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="39302A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E5DEDB"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="FFCA08"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="F8931D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="CE8D3E"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="EC7016"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="E64823"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="9C6A6A"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="2998E3"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7F723D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Corbel">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Corbel" panose="020B0503020204020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Jpan" typeface="HGｺﾞｼｯｸM"/>
+        <a:font script="Hang" typeface="HY엽서L"/>
+        <a:font script="Hans" typeface="华文楷体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Arab" typeface="Tahoma"/>
+        <a:font script="Hebr" typeface="Miriam"/>
+        <a:font script="Thai" typeface="DilleniaUPC"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -8287,26 +8336,44 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Corbel" panose="020B0503020204020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="HGｺﾞｼｯｸM"/>
+        <a:font script="Hang" typeface="HY엽서L"/>
+        <a:font script="Hans" typeface="华文楷体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Tahoma"/>
+        <a:font script="Hebr" typeface="Miriam"/>
+        <a:font script="Thai" typeface="DilleniaUPC"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Inset">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8315,66 +8382,58 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="180000"/>
+                <a:lumMod val="98000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:tint val="30000"/>
+                <a:satMod val="260000"/>
+                <a:lumMod val="84000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="100000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5040000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:shade val="75000"/>
+                <a:satMod val="120000"/>
+                <a:lumMod val="90000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="22225" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -8383,28 +8442,13 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="50800" dist="25400" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="28000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -8412,12 +8456,37 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig rig="threePt" dir="tl">
+              <a:rot lat="0" lon="0" rev="20400000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
+            <a:bevelT w="50800" h="12700" prst="softRound"/>
+          </a:sp3d>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="44450" dist="50800" dir="5400000" sx="96000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="34000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="tl">
+              <a:rot lat="0" lon="0" rev="20400000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d contourW="15875">
+            <a:bevelT w="101600" h="25400" prst="softRound"/>
+            <a:contourClr>
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:contourClr>
           </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
@@ -8429,45 +8498,39 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="90000"/>
+                <a:lumMod val="120000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="98000"/>
+                <a:satMod val="120000"/>
+                <a:lumMod val="98000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
+                <a:tint val="90000"/>
+                <a:satMod val="92000"/>
+                <a:lumMod val="120000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
+                <a:shade val="98000"/>
+                <a:satMod val="120000"/>
+                <a:lumMod val="98000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+            <a:fillToRect l="50000" t="50000" r="100000" b="100000"/>
           </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -8475,29 +8538,35 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Wisp" id="{7CB32D59-10C0-40DD-B7BD-2E94284A981C}" vid="{24B1A44C-C006-48B2-A4D7-E5549B3D8CD4}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1001"/>
+  <dimension ref="A1:O1001"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.21875" customWidth="1"/>
+    <col min="9" max="9" width="7.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8535,7 +8604,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -8573,7 +8642,7 @@
         <v>80469</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -8611,7 +8680,7 @@
         <v>178443</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -8649,7 +8718,7 @@
         <v>66560</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -8687,7 +8756,7 @@
         <v>8835</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -8725,7 +8794,7 @@
         <v>11392</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -8763,7 +8832,7 @@
         <v>130921</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -8801,7 +8870,7 @@
         <v>38560</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -8839,7 +8908,7 @@
         <v>106323</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -8876,8 +8945,11 @@
       <c r="L10">
         <v>24558</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O10" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -8914,8 +8986,15 @@
       <c r="L11">
         <v>56704</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <f>VLOOKUP(N11,A1:L16,12,FALSE)</f>
+        <v>106323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -8953,7 +9032,7 @@
         <v>11790</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -8991,7 +9070,7 @@
         <v>177660</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -9029,7 +9108,7 @@
         <v>95715</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -9066,8 +9145,12 @@
       <c r="L15">
         <v>37709</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O15" t="str">
+        <f>HLOOKUP(G1,A1:L22,5,FALSE)</f>
+        <v>Gandhidham</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -46536,6 +46619,6798 @@
       </c>
     </row>
   </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{554D4A35-920F-4EF4-A143-68894776BCD6}" scale="130" showPageBreaks="1" topLeftCell="C15">
+      <selection activeCell="B1" sqref="B1:L35"/>
+      <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup orientation="landscape" r:id="rId1"/>
+    </customSheetView>
+  </customSheetViews>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N11" xr:uid="{A962A179-3E4E-4AC3-AA12-E32D788806AF}">
+      <formula1>$A$2:$A$11</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13DE970A-D218-403D-AA97-7C36718DB5BB}">
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3896</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2383</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2661</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2686</v>
+      </c>
+      <c r="K2">
+        <v>7792</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2945</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2355</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2656</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J3" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K3">
+        <v>8835</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>2848</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F4" t="s">
+        <v>2356</v>
+      </c>
+      <c r="G4" t="s">
+        <v>2657</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2686</v>
+      </c>
+      <c r="K4">
+        <v>11392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2877</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F5" t="s">
+        <v>2369</v>
+      </c>
+      <c r="G5" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J5" t="s">
+        <v>2689</v>
+      </c>
+      <c r="K5">
+        <v>11508</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>11790</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2662</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I6" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2688</v>
+      </c>
+      <c r="K6">
+        <v>11790</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2081</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F7" t="s">
+        <v>2371</v>
+      </c>
+      <c r="G7" t="s">
+        <v>2661</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I7" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J7" t="s">
+        <v>2689</v>
+      </c>
+      <c r="K7">
+        <v>12486</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>4246</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2372</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2665</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I8" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2689</v>
+      </c>
+      <c r="K8">
+        <v>16984</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>3080</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2358</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2655</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I9" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J9" t="s">
+        <v>2689</v>
+      </c>
+      <c r="K9">
+        <v>18480</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>7262</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F10" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G10" t="s">
+        <v>2654</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I10" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J10" t="s">
+        <v>2689</v>
+      </c>
+      <c r="K10">
+        <v>21786</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>4093</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F11" t="s">
+        <v>2360</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2658</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I11" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J11" t="s">
+        <v>2688</v>
+      </c>
+      <c r="K11">
+        <v>24558</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>7947</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F12" t="s">
+        <v>2380</v>
+      </c>
+      <c r="G12" t="s">
+        <v>2670</v>
+      </c>
+      <c r="H12" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I12" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J12" t="s">
+        <v>2686</v>
+      </c>
+      <c r="K12">
+        <v>31788</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>8325</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F13" t="s">
+        <v>2379</v>
+      </c>
+      <c r="G13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="H13" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I13" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J13" t="s">
+        <v>2689</v>
+      </c>
+      <c r="K13">
+        <v>33300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>5387</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F14" t="s">
+        <v>2365</v>
+      </c>
+      <c r="G14" t="s">
+        <v>2664</v>
+      </c>
+      <c r="H14" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I14" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J14" t="s">
+        <v>2687</v>
+      </c>
+      <c r="K14">
+        <v>37709</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>9640</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F15" t="s">
+        <v>2358</v>
+      </c>
+      <c r="G15" t="s">
+        <v>2659</v>
+      </c>
+      <c r="H15" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I15" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J15" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K15">
+        <v>38560</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>13195</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2378</v>
+      </c>
+      <c r="G16" t="s">
+        <v>2665</v>
+      </c>
+      <c r="H16" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I16" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J16" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K16">
+        <v>39585</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>5670</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F17" t="s">
+        <v>2378</v>
+      </c>
+      <c r="G17" t="s">
+        <v>2670</v>
+      </c>
+      <c r="H17" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I17" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J17" t="s">
+        <v>2689</v>
+      </c>
+      <c r="K17">
+        <v>45360</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>6274</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F18" t="s">
+        <v>2377</v>
+      </c>
+      <c r="G18" t="s">
+        <v>2660</v>
+      </c>
+      <c r="H18" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I18" t="s">
+        <v>2692</v>
+      </c>
+      <c r="J18" t="s">
+        <v>2689</v>
+      </c>
+      <c r="K18">
+        <v>50192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>7088</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F19" t="s">
+        <v>2361</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2661</v>
+      </c>
+      <c r="H19" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J19" t="s">
+        <v>2688</v>
+      </c>
+      <c r="K19">
+        <v>56704</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>14215</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2376</v>
+      </c>
+      <c r="G20" t="s">
+        <v>2669</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I20" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J20" t="s">
+        <v>2687</v>
+      </c>
+      <c r="K20">
+        <v>56860</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>14772</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F21" t="s">
+        <v>2375</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2669</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I21" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J21" t="s">
+        <v>2686</v>
+      </c>
+      <c r="K21">
+        <v>59088</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>16640</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F22" t="s">
+        <v>2354</v>
+      </c>
+      <c r="G22" t="s">
+        <v>2655</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I22" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J22" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K22">
+        <v>66560</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>7785</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2367</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2665</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I23" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J23" t="s">
+        <v>2687</v>
+      </c>
+      <c r="K23">
+        <v>70065</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>14316</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F24" t="s">
+        <v>2373</v>
+      </c>
+      <c r="G24" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H24" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I24" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J24" t="s">
+        <v>2688</v>
+      </c>
+      <c r="K24">
+        <v>71580</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>9997</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2370</v>
+      </c>
+      <c r="G25" t="s">
+        <v>2667</v>
+      </c>
+      <c r="H25" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I25" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J25" t="s">
+        <v>2687</v>
+      </c>
+      <c r="K25">
+        <v>79976</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>8941</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F26" t="s">
+        <v>2352</v>
+      </c>
+      <c r="G26" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I26" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J26" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K26">
+        <v>80469</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>11358</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F27" t="s">
+        <v>2381</v>
+      </c>
+      <c r="G27" t="s">
+        <v>2672</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I27" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J27" t="s">
+        <v>2688</v>
+      </c>
+      <c r="K27">
+        <v>90864</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>19143</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F28" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G28" t="s">
+        <v>2663</v>
+      </c>
+      <c r="H28" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I28" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J28" t="s">
+        <v>2688</v>
+      </c>
+      <c r="K28">
+        <v>95715</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>15189</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F29" t="s">
+        <v>2359</v>
+      </c>
+      <c r="G29" t="s">
+        <v>2660</v>
+      </c>
+      <c r="H29" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I29" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J29" t="s">
+        <v>2687</v>
+      </c>
+      <c r="K29">
+        <v>106323</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>18074</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F30" t="s">
+        <v>2374</v>
+      </c>
+      <c r="G30" t="s">
+        <v>2668</v>
+      </c>
+      <c r="H30" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I30" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J30" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K30">
+        <v>108444</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>19724</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F31" t="s">
+        <v>2366</v>
+      </c>
+      <c r="G31" t="s">
+        <v>2656</v>
+      </c>
+      <c r="H31" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I31" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J31" t="s">
+        <v>2687</v>
+      </c>
+      <c r="K31">
+        <v>118344</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32">
+        <v>15744</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F32" t="s">
+        <v>2382</v>
+      </c>
+      <c r="G32" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H32" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I32" t="s">
+        <v>2683</v>
+      </c>
+      <c r="J32" t="s">
+        <v>2687</v>
+      </c>
+      <c r="K32">
+        <v>125952</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>18703</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F33" t="s">
+        <v>2357</v>
+      </c>
+      <c r="G33" t="s">
+        <v>2658</v>
+      </c>
+      <c r="H33" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I33" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J33" t="s">
+        <v>2686</v>
+      </c>
+      <c r="K33">
+        <v>130921</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34">
+        <v>19740</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F34" t="s">
+        <v>2363</v>
+      </c>
+      <c r="G34" t="s">
+        <v>2661</v>
+      </c>
+      <c r="H34" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I34" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J34" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K34">
+        <v>177660</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B35">
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>19827</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F35" t="s">
+        <v>2353</v>
+      </c>
+      <c r="G35" t="s">
+        <v>2654</v>
+      </c>
+      <c r="H35" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I35" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J35" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K35">
+        <v>178443</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>2693</v>
+      </c>
+      <c r="B37">
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>89900</v>
+      </c>
+      <c r="D37" s="8">
+        <v>46178</v>
+      </c>
+      <c r="E37" t="s">
+        <v>2694</v>
+      </c>
+      <c r="K37" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K35" xr:uid="{BAB4811E-3F89-4BB4-9F3B-EB727835F6B2}"/>
+  <customSheetViews>
+    <customSheetView guid="{554D4A35-920F-4EF4-A143-68894776BCD6}" scale="85" showAutoFilter="1" hiddenRows="1">
+      <selection activeCell="N19" sqref="N19"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="A1:K35" xr:uid="{00000000-0000-0000-0000-000000000000}"/>
+    </customSheetView>
+  </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34954B-0747-48D9-B711-DF998E31C379}">
+  <dimension ref="A1:D391"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>8941</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>19827</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>16640</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>2945</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>2848</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>18703</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>9640</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>15189</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>4093</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <v>7088</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>11790</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>19740</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <v>19143</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>5387</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>19724</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>7785</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>7262</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>2877</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <v>9997</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>2081</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>4246</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <v>14316</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="6">
+        <v>18074</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="6">
+        <v>14772</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <v>14215</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
+        <v>6274</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
+        <v>5670</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
+        <v>8325</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <v>13195</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="6">
+        <v>7947</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="6">
+        <v>11358</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="6">
+        <v>15744</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="6">
+        <v>3080</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="6">
+        <v>3896</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="6">
+        <v>12383</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="6">
+        <v>10823</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="6">
+        <v>5049</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="6">
+        <v>12548</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="6">
+        <v>8432</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="6">
+        <v>13351</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="6">
+        <v>16286</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="6">
+        <v>4978</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="6">
+        <v>10629</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="6">
+        <v>7312</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="6">
+        <v>5963</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="6">
+        <v>4437</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="6">
+        <v>9000</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="6">
+        <v>4321</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="6">
+        <v>12180</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="6">
+        <v>4360</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="6">
+        <v>12400</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="6">
+        <v>15553</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="6">
+        <v>2337</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="6">
+        <v>18457</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="6">
+        <v>19124</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="6">
+        <v>5248</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="6">
+        <v>2739</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="6">
+        <v>15728</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="6">
+        <v>7390</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="6">
+        <v>10604</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="6">
+        <v>6267</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="6">
+        <v>15409</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="6">
+        <v>18562</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="6">
+        <v>12242</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="6">
+        <v>10977</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="6">
+        <v>19091</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="6">
+        <v>11557</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="6">
+        <v>16181</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="6">
+        <v>17480</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="6">
+        <v>16998</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="6">
+        <v>7330</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="6">
+        <v>11015</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="6">
+        <v>12417</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="6">
+        <v>17469</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="6">
+        <v>12483</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="6">
+        <v>16926</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="6">
+        <v>6754</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="6">
+        <v>13385</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="6">
+        <v>12587</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="6">
+        <v>7612</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="6">
+        <v>10397</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="6">
+        <v>13106</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="6">
+        <v>8957</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="6">
+        <v>5792</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="6">
+        <v>12305</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="6">
+        <v>16608</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="6">
+        <v>8445</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="6">
+        <v>8363</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="6">
+        <v>2165</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="6">
+        <v>18818</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="6">
+        <v>16744</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="6">
+        <v>3968</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="6">
+        <v>3228</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="6">
+        <v>11220</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="6">
+        <v>3198</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="6">
+        <v>13505</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="6">
+        <v>16730</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="6">
+        <v>9579</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="6">
+        <v>5406</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="6">
+        <v>6966</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="6">
+        <v>7517</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="6">
+        <v>9197</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="6">
+        <v>11166</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="6">
+        <v>19611</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="6">
+        <v>14767</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="6">
+        <v>9278</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="6">
+        <v>3492</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="6">
+        <v>5767</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="6">
+        <v>17101</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="6">
+        <v>19538</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="6">
+        <v>2184</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="6">
+        <v>9278</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="6">
+        <v>13974</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="6">
+        <v>7074</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="6">
+        <v>12430</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="6">
+        <v>9726</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="6">
+        <v>15051</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="6">
+        <v>7209</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="6">
+        <v>8462</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="6">
+        <v>18677</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="6">
+        <v>16495</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="6">
+        <v>6983</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="6">
+        <v>10092</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="6">
+        <v>11576</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="6">
+        <v>14271</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="6">
+        <v>5869</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="6">
+        <v>5796</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="6">
+        <v>7393</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="6">
+        <v>13943</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="6">
+        <v>3506</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="6">
+        <v>17920</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="6">
+        <v>16550</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="6">
+        <v>9213</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="6">
+        <v>3146</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="6">
+        <v>4737</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="6">
+        <v>17708</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="6">
+        <v>19729</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="6">
+        <v>3365</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="6">
+        <v>15856</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="6">
+        <v>18371</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="6">
+        <v>4170</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="6">
+        <v>7222</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="6">
+        <v>18473</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="6">
+        <v>5185</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="6">
+        <v>10347</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="6">
+        <v>3537</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="6">
+        <v>4313</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="6">
+        <v>14403</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="6">
+        <v>3873</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="6">
+        <v>14683</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="6">
+        <v>4295</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="6">
+        <v>7955</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="6">
+        <v>19700</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="6">
+        <v>10211</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="6">
+        <v>3007</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="6">
+        <v>6820</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="6">
+        <v>18062</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="6">
+        <v>18592</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="6">
+        <v>4233</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="6">
+        <v>18005</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="6">
+        <v>4326</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="6">
+        <v>19800</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="6">
+        <v>3193</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="6">
+        <v>12058</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="6">
+        <v>11820</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="6">
+        <v>17455</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="6">
+        <v>2907</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="6">
+        <v>18475</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="6">
+        <v>14871</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="6">
+        <v>17223</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="6">
+        <v>3097</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="6">
+        <v>14428</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="6">
+        <v>4792</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="6">
+        <v>16317</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="6">
+        <v>13791</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="6">
+        <v>11220</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="6">
+        <v>3716</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="6">
+        <v>16402</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="6">
+        <v>9533</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="6">
+        <v>5333</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="6">
+        <v>10527</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="6">
+        <v>14111</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="6">
+        <v>17321</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="6">
+        <v>2662</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="6">
+        <v>16809</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="6">
+        <v>11433</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" s="6">
+        <v>9998</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" s="6">
+        <v>10989</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" s="6">
+        <v>11993</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" s="6">
+        <v>13133</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" s="6">
+        <v>13111</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193" s="6">
+        <v>5794</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194" s="6">
+        <v>9752</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" s="6">
+        <v>18639</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="6">
+        <v>8770</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" s="6">
+        <v>8385</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" s="6">
+        <v>11527</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" s="6">
+        <v>18074</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" s="6">
+        <v>7400</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" s="6">
+        <v>3677</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" s="6">
+        <v>8149</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203" s="6">
+        <v>7735</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A204" s="6">
+        <v>17409</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A205" s="6">
+        <v>19765</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A206" s="6">
+        <v>6248</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A207" s="6">
+        <v>14351</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A208" s="6">
+        <v>3565</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" s="6">
+        <v>6593</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210" s="6">
+        <v>12602</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A211" s="6">
+        <v>5339</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A212" s="6">
+        <v>9615</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A213" s="6">
+        <v>11504</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A214" s="6">
+        <v>8337</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A215" s="6">
+        <v>7241</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A216" s="6">
+        <v>18757</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A217" s="6">
+        <v>2833</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A218" s="6">
+        <v>16074</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A219" s="6">
+        <v>4073</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A220" s="6">
+        <v>14236</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A221" s="6">
+        <v>8216</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A222" s="6">
+        <v>16860</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A223" s="6">
+        <v>4968</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A224" s="6">
+        <v>14435</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225" s="6">
+        <v>19332</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A226" s="6">
+        <v>17452</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227" s="6">
+        <v>7347</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A228" s="6">
+        <v>14323</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229" s="6">
+        <v>4257</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230" s="6">
+        <v>3175</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231" s="6">
+        <v>12301</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232" s="6">
+        <v>19589</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233" s="6">
+        <v>7549</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234" s="6">
+        <v>12350</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235" s="6">
+        <v>7779</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236" s="6">
+        <v>3258</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A237" s="6">
+        <v>3901</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A238" s="6">
+        <v>7042</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A239" s="6">
+        <v>17937</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A240" s="6">
+        <v>18978</v>
+      </c>
+      <c r="B240" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A241" s="6">
+        <v>19870</v>
+      </c>
+      <c r="B241" s="7" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D241" s="6" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A242" s="6">
+        <v>2101</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A243" s="6">
+        <v>16920</v>
+      </c>
+      <c r="B243" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D243" s="6" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A244" s="6">
+        <v>8834</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D244" s="6" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A245" s="6">
+        <v>12274</v>
+      </c>
+      <c r="B245" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A246" s="6">
+        <v>19370</v>
+      </c>
+      <c r="B246" s="7" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A247" s="6">
+        <v>10715</v>
+      </c>
+      <c r="B247" s="7" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D247" s="6" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A248" s="6">
+        <v>5211</v>
+      </c>
+      <c r="B248" s="7" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D248" s="6" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A249" s="6">
+        <v>12600</v>
+      </c>
+      <c r="B249" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D249" s="6" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A250" s="6">
+        <v>8564</v>
+      </c>
+      <c r="B250" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A251" s="6">
+        <v>7936</v>
+      </c>
+      <c r="B251" s="7" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D251" s="6" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A252" s="6">
+        <v>16941</v>
+      </c>
+      <c r="B252" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D252" s="6" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A253" s="6">
+        <v>7666</v>
+      </c>
+      <c r="B253" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D253" s="6" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254" s="6">
+        <v>15002</v>
+      </c>
+      <c r="B254" s="7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A255" s="6">
+        <v>5532</v>
+      </c>
+      <c r="B255" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D255" s="6" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A256" s="6">
+        <v>4801</v>
+      </c>
+      <c r="B256" s="7" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D256" s="6" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A257" s="6">
+        <v>9463</v>
+      </c>
+      <c r="B257" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D257" s="6" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A258" s="6">
+        <v>7103</v>
+      </c>
+      <c r="B258" s="7" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D258" s="6" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A259" s="6">
+        <v>2075</v>
+      </c>
+      <c r="B259" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D259" s="6" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A260" s="6">
+        <v>3966</v>
+      </c>
+      <c r="B260" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D260" s="6" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A261" s="6">
+        <v>14201</v>
+      </c>
+      <c r="B261" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A262" s="6">
+        <v>6090</v>
+      </c>
+      <c r="B262" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D262" s="6" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A263" s="6">
+        <v>5715</v>
+      </c>
+      <c r="B263" s="7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A264" s="6">
+        <v>17679</v>
+      </c>
+      <c r="B264" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D264" s="6" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A265" s="6">
+        <v>17168</v>
+      </c>
+      <c r="B265" s="7" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D265" s="6" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A266" s="6">
+        <v>9949</v>
+      </c>
+      <c r="B266" s="7" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D266" s="6" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A267" s="6">
+        <v>5878</v>
+      </c>
+      <c r="B267" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D267" s="6" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A268" s="6">
+        <v>6356</v>
+      </c>
+      <c r="B268" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D268" s="6" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A269" s="6">
+        <v>16851</v>
+      </c>
+      <c r="B269" s="7" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D269" s="6" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A270" s="6">
+        <v>5216</v>
+      </c>
+      <c r="B270" s="7" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D270" s="6" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A271" s="6">
+        <v>4430</v>
+      </c>
+      <c r="B271" s="7" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D271" s="6" t="s">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A272" s="6">
+        <v>10856</v>
+      </c>
+      <c r="B272" s="7" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A273" s="6">
+        <v>11483</v>
+      </c>
+      <c r="B273" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D273" s="6" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A274" s="6">
+        <v>11435</v>
+      </c>
+      <c r="B274" s="7" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D274" s="6" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A275" s="6">
+        <v>7000</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A276" s="6">
+        <v>8438</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D276" s="6" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A277" s="6">
+        <v>3588</v>
+      </c>
+      <c r="B277" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A278" s="6">
+        <v>17679</v>
+      </c>
+      <c r="B278" s="7" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D278" s="6" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A279" s="6">
+        <v>13157</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D279" s="6" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A280" s="6">
+        <v>10947</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A281" s="6">
+        <v>16539</v>
+      </c>
+      <c r="B281" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D281" s="6" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A282" s="6">
+        <v>12975</v>
+      </c>
+      <c r="B282" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A283" s="6">
+        <v>18694</v>
+      </c>
+      <c r="B283" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D283" s="6" t="s">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284" s="6">
+        <v>18243</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285" s="6">
+        <v>15747</v>
+      </c>
+      <c r="B285" s="7" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286" s="6">
+        <v>17443</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287" s="6">
+        <v>18685</v>
+      </c>
+      <c r="B287" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288" s="6">
+        <v>17727</v>
+      </c>
+      <c r="B288" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289" s="6">
+        <v>3339</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290" s="6">
+        <v>19562</v>
+      </c>
+      <c r="B290" s="7" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A291" s="6">
+        <v>5704</v>
+      </c>
+      <c r="B291" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A292" s="6">
+        <v>7774</v>
+      </c>
+      <c r="B292" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A293" s="6">
+        <v>2513</v>
+      </c>
+      <c r="B293" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A294" s="6">
+        <v>5574</v>
+      </c>
+      <c r="B294" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A295" s="6">
+        <v>16767</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A296" s="6">
+        <v>9548</v>
+      </c>
+      <c r="B296" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D296" s="6" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A297" s="6">
+        <v>13382</v>
+      </c>
+      <c r="B297" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A298" s="6">
+        <v>10004</v>
+      </c>
+      <c r="B298" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A299" s="6">
+        <v>19610</v>
+      </c>
+      <c r="B299" s="7" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D299" s="6" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A300" s="6">
+        <v>2106</v>
+      </c>
+      <c r="B300" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D300" s="6" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A301" s="6">
+        <v>9659</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A302" s="6">
+        <v>15918</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D302" s="6" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A303" s="6">
+        <v>6352</v>
+      </c>
+      <c r="B303" s="7" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A304" s="6">
+        <v>11809</v>
+      </c>
+      <c r="B304" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D304" s="6" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A305" s="6">
+        <v>17147</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D305" s="6" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A306" s="6">
+        <v>7046</v>
+      </c>
+      <c r="B306" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D306" s="6" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A307" s="6">
+        <v>10982</v>
+      </c>
+      <c r="B307" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A308" s="6">
+        <v>17135</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A309" s="6">
+        <v>14660</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A310" s="6">
+        <v>17394</v>
+      </c>
+      <c r="B310" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A311" s="6">
+        <v>5396</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D311" s="6" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A312" s="6">
+        <v>5962</v>
+      </c>
+      <c r="B312" s="7" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D312" s="6" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A313" s="6">
+        <v>19214</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D313" s="6" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A314" s="6">
+        <v>5876</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D314" s="6" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A315" s="6">
+        <v>10913</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D315" s="6" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A316" s="6">
+        <v>12480</v>
+      </c>
+      <c r="B316" s="7" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D316" s="6" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A317" s="6">
+        <v>17727</v>
+      </c>
+      <c r="B317" s="7" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D317" s="6" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A318" s="6">
+        <v>10390</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D318" s="6" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A319" s="6">
+        <v>5504</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D319" s="6" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A320" s="6">
+        <v>4441</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D320" s="6" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A321" s="6">
+        <v>2469</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D321" s="6" t="s">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A322" s="6">
+        <v>16857</v>
+      </c>
+      <c r="B322" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D322" s="6" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A323" s="6">
+        <v>9160</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C323" s="6" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D323" s="6" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A324" s="6">
+        <v>3188</v>
+      </c>
+      <c r="B324" s="7" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C324" s="6" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D324" s="6" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A325" s="6">
+        <v>10476</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D325" s="6" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A326" s="6">
+        <v>17424</v>
+      </c>
+      <c r="B326" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C326" s="6" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D326" s="6" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A327" s="6">
+        <v>19354</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A328" s="6">
+        <v>15180</v>
+      </c>
+      <c r="B328" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C328" s="6" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D328" s="6" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A329" s="6">
+        <v>4469</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D329" s="6" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A330" s="6">
+        <v>9255</v>
+      </c>
+      <c r="B330" s="7" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C330" s="6" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D330" s="6" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A331" s="6">
+        <v>3758</v>
+      </c>
+      <c r="B331" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C331" s="6" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D331" s="6" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A332" s="6">
+        <v>6049</v>
+      </c>
+      <c r="B332" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C332" s="6" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D332" s="6" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A333" s="6">
+        <v>18495</v>
+      </c>
+      <c r="B333" s="7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C333" s="6" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D333" s="6" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A334" s="6">
+        <v>16306</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C334" s="6" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D334" s="6" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A335" s="6">
+        <v>8992</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D335" s="6" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A336" s="6">
+        <v>3779</v>
+      </c>
+      <c r="B336" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D336" s="6" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A337" s="6">
+        <v>6690</v>
+      </c>
+      <c r="B337" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D337" s="6" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A338" s="6">
+        <v>4538</v>
+      </c>
+      <c r="B338" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C338" s="6" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D338" s="6" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A339" s="6">
+        <v>14316</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D339" s="6" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A340" s="6">
+        <v>3827</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D340" s="6" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A341" s="6">
+        <v>14058</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A342" s="6">
+        <v>5441</v>
+      </c>
+      <c r="B342" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D342" s="6" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A343" s="6">
+        <v>7479</v>
+      </c>
+      <c r="B343" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A344" s="6">
+        <v>7674</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C344" s="6" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D344" s="6" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A345" s="6">
+        <v>11299</v>
+      </c>
+      <c r="B345" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D345" s="6" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A346" s="6">
+        <v>13466</v>
+      </c>
+      <c r="B346" s="7" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C346" s="6" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D346" s="6" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A347" s="6">
+        <v>19627</v>
+      </c>
+      <c r="B347" s="7" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C347" s="6" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D347" s="6" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A348" s="6">
+        <v>6835</v>
+      </c>
+      <c r="B348" s="7" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D348" s="6" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A349" s="6">
+        <v>17179</v>
+      </c>
+      <c r="B349" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D349" s="6" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A350" s="6">
+        <v>14019</v>
+      </c>
+      <c r="B350" s="7" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C350" s="6" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D350" s="6" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A351" s="6">
+        <v>5454</v>
+      </c>
+      <c r="B351" s="7" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D351" s="6" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A352" s="6">
+        <v>7945</v>
+      </c>
+      <c r="B352" s="7" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D352" s="6" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A353" s="6">
+        <v>5901</v>
+      </c>
+      <c r="B353" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D353" s="6" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A354" s="6">
+        <v>5881</v>
+      </c>
+      <c r="B354" s="7" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D354" s="6" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A355" s="6">
+        <v>9831</v>
+      </c>
+      <c r="B355" s="7" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D355" s="6" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A356" s="6">
+        <v>4792</v>
+      </c>
+      <c r="B356" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D356" s="6" t="s">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A357" s="6">
+        <v>7940</v>
+      </c>
+      <c r="B357" s="7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D357" s="6" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A358" s="6">
+        <v>2279</v>
+      </c>
+      <c r="B358" s="7" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D358" s="6" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A359" s="6">
+        <v>11338</v>
+      </c>
+      <c r="B359" s="7" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D359" s="6" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A360" s="6">
+        <v>13817</v>
+      </c>
+      <c r="B360" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D360" s="6" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A361" s="6">
+        <v>15116</v>
+      </c>
+      <c r="B361" s="7" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D361" s="6" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A362" s="6">
+        <v>2815</v>
+      </c>
+      <c r="B362" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C362" s="6" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D362" s="6" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A363" s="6">
+        <v>11871</v>
+      </c>
+      <c r="B363" s="7" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C363" s="6" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D363" s="6" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A364" s="6">
+        <v>8081</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D364" s="6" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A365" s="6">
+        <v>4654</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C365" s="6" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D365" s="6" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A366" s="6">
+        <v>12213</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D366" s="6" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A367" s="6">
+        <v>19194</v>
+      </c>
+      <c r="B367" s="7" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C367" s="6" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D367" s="6" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A368" s="6">
+        <v>2512</v>
+      </c>
+      <c r="B368" s="7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C368" s="6" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D368" s="6" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A369" s="6">
+        <v>6829</v>
+      </c>
+      <c r="B369" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C369" s="6" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D369" s="6" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A370" s="6">
+        <v>5139</v>
+      </c>
+      <c r="B370" s="7" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D370" s="6" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A371" s="6">
+        <v>6383</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C371" s="6" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D371" s="6" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A372" s="6">
+        <v>4845</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C372" s="6" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D372" s="6" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A373" s="6">
+        <v>8160</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C373" s="6" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D373" s="6" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A374" s="6">
+        <v>13749</v>
+      </c>
+      <c r="B374" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C374" s="6" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D374" s="6" t="s">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A375" s="6">
+        <v>5409</v>
+      </c>
+      <c r="B375" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C375" s="6" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D375" s="6" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A376" s="6">
+        <v>13063</v>
+      </c>
+      <c r="B376" s="7" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D376" s="6" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A377" s="6">
+        <v>6989</v>
+      </c>
+      <c r="B377" s="7" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C377" s="6" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D377" s="6" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A378" s="6">
+        <v>11515</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D378" s="6" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A379" s="6">
+        <v>8467</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D379" s="6" t="s">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A380" s="6">
+        <v>14820</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D380" s="6" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A381" s="6">
+        <v>14763</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D381" s="6" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A382" s="6">
+        <v>2511</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D382" s="6" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A383" s="6">
+        <v>15788</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C383" s="6" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D383" s="6" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A384" s="6">
+        <v>6366</v>
+      </c>
+      <c r="B384" s="7" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D384" s="6" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A385" s="6">
+        <v>18654</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D385" s="6" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A386" s="6">
+        <v>17843</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D386" s="6" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A387" s="6">
+        <v>2447</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C387" s="6" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D387" s="6" t="s">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A388" s="6">
+        <v>6469</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C388" s="6" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D388" s="6" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A389" s="6">
+        <v>18102</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C389" s="6" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D389" s="6" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A390" s="6">
+        <v>2043</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C390" s="6" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D390" s="6" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A391" s="6">
+        <v>9526</v>
+      </c>
+      <c r="B391" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C391" s="6" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D391" s="6" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+  </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{554D4A35-920F-4EF4-A143-68894776BCD6}" scale="145" showPageBreaks="1">
+      <selection activeCell="G11" sqref="G11"/>
+      <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+      <printOptions headings="1" gridLines="1"/>
+      <pageSetup scale="130" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+    </customSheetView>
+  </customSheetViews>
+  <printOptions headings="1" gridLines="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="130" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>